--- a/fianl.xlsx
+++ b/fianl.xlsx
@@ -15,11 +15,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={06e9c235-49e1-445b-ad14-9299807c00c1}</author>
-    <author>tc={8c288fc1-e849-44fd-8ec3-e3eb5160234f}</author>
+    <author>tc={63d52799-d727-43cd-be68-dcd7fde7e657}</author>
+    <author>tc={a3735f0e-cec8-4fa6-91ef-111dcc74cf12}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{06e9c235-49e1-445b-ad14-9299807c00c1}" ref="A1">
+    <comment authorId="0" xr:uid="{63d52799-d727-43cd-be68-dcd7fde7e657}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -28,7 +28,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{8c288fc1-e849-44fd-8ec3-e3eb5160234f}" ref="A1">
+    <comment authorId="1" xr:uid="{a3735f0e-cec8-4fa6-91ef-111dcc74cf12}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -44,34 +44,79 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={00754f08-030c-443a-96b7-1f90b44c035c}</author>
-    <author>tc={180e5f80-0f99-465d-aeb8-5f33b703a8da}</author>
-    <author>tc={2530cb90-77d0-4225-8b87-5549bead3c80}</author>
-    <author>tc={28fb4e7d-cb5d-4d77-88d0-d51383682362}</author>
-    <author>tc={373c0738-96a6-48cf-b5f4-31dea957134a}</author>
-    <author>tc={3984996c-de65-4413-8f8b-7c1943327248}</author>
-    <author>tc={3aceb880-1b08-4db1-a1ac-4ea4b1bcc470}</author>
-    <author>tc={50624453-ed97-40cc-91fc-3d25638dc6b9}</author>
-    <author>tc={51bacf10-e5fa-4c58-9333-c0b6dae0805d}</author>
-    <author>tc={5793895e-b99f-4827-bb5d-27a99d333e5d}</author>
-    <author>tc={5e39a9bf-5952-456e-8041-c356b89ea94c}</author>
-    <author>tc={6c2f1a4d-5692-469c-93cf-2bd99f113aec}</author>
-    <author>tc={7adfe208-3130-44a0-9f4d-0fb1c1850458}</author>
-    <author>tc={7ef3d4c1-a29c-4a4c-9d80-3306b1e9bcb5}</author>
-    <author>tc={8141c568-121a-4ec9-a95d-8e2100da1cec}</author>
-    <author>tc={87a67a64-e46a-4f8e-bfec-7d7aed281e71}</author>
-    <author>tc={8b7d8015-ed46-406d-9378-3c8634596926}</author>
-    <author>tc={97eb5bb9-d623-4ac2-9140-5cba7448b912}</author>
-    <author>tc={9a5a8381-0b2f-435c-8e7f-da7b8bdf0452}</author>
-    <author>tc={b82034be-dc46-4b4c-b506-6e738b06070e}</author>
-    <author>tc={b9c7f014-dda7-4924-a30e-6ea6ff1fc5da}</author>
-    <author>tc={c95b624b-6094-4cd0-9e1a-1db76a955c5c}</author>
-    <author>tc={f242f38a-e7fc-4a6f-ba2d-dd49ee03404c}</author>
-    <author>tc={f662b67a-6c34-4760-8f44-1e7efb7cbba7}</author>
-    <author>tc={fddd98d9-35f0-42e9-8589-424099660817}</author>
+    <author>tc={011fd032-94f4-4833-967f-304817de3267}</author>
+    <author>tc={0ca4a076-72d1-46fc-94b1-adc0329cd557}</author>
+    <author>tc={18863187-a8de-455d-9379-060c04b24aad}</author>
+    <author>tc={191a5d8b-da35-46af-b884-e11080df99bc}</author>
+    <author>tc={1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}</author>
+    <author>tc={260b74e2-c79b-4313-9bbe-dc58d0bd867f}</author>
+    <author>tc={32eada8a-3806-4748-abd4-edd0714f7be0}</author>
+    <author>tc={34474ebd-51a2-4bd6-b5e7-e05f3b571e27}</author>
+    <author>tc={3495ca3d-131a-4d92-8e4a-f39d30d48d39}</author>
+    <author>tc={367ac776-ff23-4107-a3da-66a734b6359d}</author>
+    <author>tc={3bcbe15d-7181-4d69-82b7-b54610d3c1ae}</author>
+    <author>tc={55e228b8-6949-499c-a454-81f0501833b3}</author>
+    <author>tc={5e904548-7fec-4891-b6f5-23d22093d3f6}</author>
+    <author>tc={68a5be20-8c63-4013-b0e5-c37a35a49cc2}</author>
+    <author>tc={6e877e43-b507-481e-8b91-012db4e74917}</author>
+    <author>tc={796f1b4b-3dec-4fca-a1c0-a91ad83df44f}</author>
+    <author>tc={883914c5-7ce1-44b0-992a-c2d83e3b1a81}</author>
+    <author>tc={b54dbb6b-1a8b-4105-a84d-36b5794aa5de}</author>
+    <author>tc={daa26dd0-ec64-4846-ab9c-83cae74a5d36}</author>
+    <author>tc={e0b710dc-ddc9-420a-89a0-f58422177788}</author>
+    <author>tc={e50642f5-662b-492e-8317-3e200d3d3550}</author>
+    <author>tc={eae5a438-f943-4aac-8104-2d5447116caf}</author>
+    <author>tc={eaf9c939-f963-4570-be66-42717b46b409}</author>
+    <author>tc={eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}</author>
+    <author>tc={f5c155c2-d59b-4500-b951-4f3555a635ee}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{00754f08-030c-443a-96b7-1f90b44c035c}" ref="E32">
+    <comment authorId="0" xr:uid="{011fd032-94f4-4833-967f-304817de3267}" ref="E59">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	WRONG!!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{0ca4a076-72d1-46fc-94b1-adc0329cd557}" ref="E96">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{18863187-a8de-455d-9379-060c04b24aad}" ref="E87">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	UI
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{191a5d8b-da35-46af-b884-e11080df99bc}" ref="E36">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	WRONG!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}" ref="E102">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{260b74e2-c79b-4313-9bbe-dc58d0bd867f}" ref="E32">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +125,52 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{180e5f80-0f99-465d-aeb8-5f33b703a8da}" ref="E74">
+    <comment authorId="6" xr:uid="{32eada8a-3806-4748-abd4-edd0714f7be0}" ref="E98">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{34474ebd-51a2-4bd6-b5e7-e05f3b571e27}" ref="E97">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{3495ca3d-131a-4d92-8e4a-f39d30d48d39}" ref="E22">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	filtered notif
+</t>
+      </text>
+    </comment>
+    <comment authorId="9" xr:uid="{367ac776-ff23-4107-a3da-66a734b6359d}" ref="E91">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	combine 87,88,89
+</t>
+      </text>
+    </comment>
+    <comment authorId="10" xr:uid="{3bcbe15d-7181-4d69-82b7-b54610d3c1ae}" ref="E57">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	to be reviewed
+</t>
+      </text>
+    </comment>
+    <comment authorId="11" xr:uid="{55e228b8-6949-499c-a454-81f0501833b3}" ref="E74">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,7 +179,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{2530cb90-77d0-4225-8b87-5549bead3c80}" ref="E79">
+    <comment authorId="12" xr:uid="{5e904548-7fec-4891-b6f5-23d22093d3f6}" ref="E79">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -98,7 +188,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{28fb4e7d-cb5d-4d77-88d0-d51383682362}" ref="E37">
+    <comment authorId="13" xr:uid="{68a5be20-8c63-4013-b0e5-c37a35a49cc2}" ref="E37">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -107,7 +197,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{373c0738-96a6-48cf-b5f4-31dea957134a}" ref="E100">
+    <comment authorId="14" xr:uid="{6e877e43-b507-481e-8b91-012db4e74917}" ref="E99">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,7 +206,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="5" xr:uid="{3984996c-de65-4413-8f8b-7c1943327248}" ref="E94">
+    <comment authorId="15" xr:uid="{796f1b4b-3dec-4fca-a1c0-a91ad83df44f}" ref="E95">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -125,7 +215,52 @@
 </t>
       </text>
     </comment>
-    <comment authorId="6" xr:uid="{3aceb880-1b08-4db1-a1ac-4ea4b1bcc470}" ref="E60">
+    <comment authorId="16" xr:uid="{883914c5-7ce1-44b0-992a-c2d83e3b1a81}" ref="E26">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	will delete
+</t>
+      </text>
+    </comment>
+    <comment authorId="17" xr:uid="{b54dbb6b-1a8b-4105-a84d-36b5794aa5de}" ref="E24">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	bulk import
+</t>
+      </text>
+    </comment>
+    <comment authorId="18" xr:uid="{daa26dd0-ec64-4846-ab9c-83cae74a5d36}" ref="E25">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ip address
+</t>
+      </text>
+    </comment>
+    <comment authorId="19" xr:uid="{e0b710dc-ddc9-420a-89a0-f58422177788}" ref="E58">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	aaaaa
+</t>
+      </text>
+    </comment>
+    <comment authorId="20" xr:uid="{e50642f5-662b-492e-8317-3e200d3d3550}" ref="E76">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong
+</t>
+      </text>
+    </comment>
+    <comment authorId="21" xr:uid="{eae5a438-f943-4aac-8104-2d5447116caf}" ref="E60">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -134,7 +269,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="7" xr:uid="{50624453-ed97-40cc-91fc-3d25638dc6b9}" ref="E102">
+    <comment authorId="22" xr:uid="{eaf9c939-f963-4570-be66-42717b46b409}" ref="E101">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -143,79 +278,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="8" xr:uid="{51bacf10-e5fa-4c58-9333-c0b6dae0805d}" ref="E25">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ip address
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{5793895e-b99f-4827-bb5d-27a99d333e5d}" ref="E58">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	aaaaa
-</t>
-      </text>
-    </comment>
-    <comment authorId="10" xr:uid="{5e39a9bf-5952-456e-8041-c356b89ea94c}" ref="E24">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	bulk import
-</t>
-      </text>
-    </comment>
-    <comment authorId="11" xr:uid="{6c2f1a4d-5692-469c-93cf-2bd99f113aec}" ref="E76">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong
-</t>
-      </text>
-    </comment>
-    <comment authorId="12" xr:uid="{7adfe208-3130-44a0-9f4d-0fb1c1850458}" ref="E22">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	filtered notif
-</t>
-      </text>
-    </comment>
-    <comment authorId="13" xr:uid="{7ef3d4c1-a29c-4a4c-9d80-3306b1e9bcb5}" ref="E99">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!
-</t>
-      </text>
-    </comment>
-    <comment authorId="14" xr:uid="{8141c568-121a-4ec9-a95d-8e2100da1cec}" ref="E36">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	WRONG!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="15" xr:uid="{87a67a64-e46a-4f8e-bfec-7d7aed281e71}" ref="E26">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	will delete
-</t>
-      </text>
-    </comment>
-    <comment authorId="16" xr:uid="{8b7d8015-ed46-406d-9378-3c8634596926}" ref="E98">
+    <comment authorId="23" xr:uid="{eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}" ref="E94">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -224,75 +287,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="17" xr:uid="{97eb5bb9-d623-4ac2-9140-5cba7448b912}" ref="E101">
+    <comment authorId="24" xr:uid="{f5c155c2-d59b-4500-b951-4f3555a635ee}" ref="E100">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	wrong!
-</t>
-      </text>
-    </comment>
-    <comment authorId="18" xr:uid="{9a5a8381-0b2f-435c-8e7f-da7b8bdf0452}" ref="E96">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="19" xr:uid="{b82034be-dc46-4b4c-b506-6e738b06070e}" ref="E91">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	combine 87,88,89
-</t>
-      </text>
-    </comment>
-    <comment authorId="20" xr:uid="{b9c7f014-dda7-4924-a30e-6ea6ff1fc5da}" ref="E57">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	to be reviewed
-</t>
-      </text>
-    </comment>
-    <comment authorId="21" xr:uid="{c95b624b-6094-4cd0-9e1a-1db76a955c5c}" ref="E59">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	WRONG!!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="22" xr:uid="{f242f38a-e7fc-4a6f-ba2d-dd49ee03404c}" ref="E95">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="23" xr:uid="{f662b67a-6c34-4760-8f44-1e7efb7cbba7}" ref="E87">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	UI
-</t>
-      </text>
-    </comment>
-    <comment authorId="24" xr:uid="{fddd98d9-35f0-42e9-8589-424099660817}" ref="E97">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
 </t>
       </text>
     </comment>
@@ -666,24 +666,24 @@
     <t>I can communicate important course information and deadlines through the platform</t>
   </si>
   <si>
+    <t>be able to get assistance and view an FAQ page</t>
+  </si>
+  <si>
+    <t>I can quickly find answers to my questions without needing external assistance</t>
+  </si>
+  <si>
+    <t>be able to manage (create, view, update, delete) the platform's Frequently Asked Questions (FAQ)</t>
+  </si>
+  <si>
+    <t>users can quickly find answers to common issues without needing to contact support.</t>
+  </si>
+  <si>
+    <t>Profiles</t>
+  </si>
+  <si>
     <t>Student</t>
   </si>
   <si>
-    <t>enroll in available courses on the platform by selecting from the course catalog</t>
-  </si>
-  <si>
-    <t>I can associate my academic coursework with my profile and projects</t>
-  </si>
-  <si>
-    <t>view all available courses in my department along with their assigned instructors</t>
-  </si>
-  <si>
-    <t>I can explore course offerings and plan my academic path</t>
-  </si>
-  <si>
-    <t>Profiles</t>
-  </si>
-  <si>
     <t>create and update my profile including my full name, contact information, bio, profile picture, academic major, semester, and social links</t>
   </si>
   <si>
@@ -1140,10 +1140,10 @@
     <t>I can leverage my academic portfolio for job applications, graduate school admissions, or professional archiving outside the platform</t>
   </si>
   <si>
-    <t>I want to view a unified dashboard of all my project contributions and summary statistics</t>
-  </si>
-  <si>
-    <t>I can analyze the full trajectory of my academic work and quantify my achievements</t>
+    <t>to get an achievement when students whose projects I have publicly endorsed are subsequently contacted by verified employers</t>
+  </si>
+  <si>
+    <t>my long-term academic supervision efforts are visibly highlighted to the university.</t>
   </si>
   <si>
     <t>39</t>
@@ -1507,14 +1507,14 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1550,8 +1550,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="basel samer" id="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" providerId="google-sheets"/>
-  <x18tc:person displayName="Omar Ahmed" id="{51111f04-29c5-459d-8381-a95c748291fc}" providerId="google-sheets"/>
+  <x18tc:person displayName="basel samer" id="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" providerId="google-sheets"/>
+  <x18tc:person displayName="Omar Ahmed" id="{dd935650-9495-4a16-a7ad-a553b6027719}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1751,10 +1751,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:28:39.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{06e9c235-49e1-445b-ad14-9299807c00c1}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:28:39.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{63d52799-d727-43cd-be68-dcd7fde7e657}" done="0">
     <x18tc:text xml:space="preserve">complicated</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:26:56.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{8c288fc1-e849-44fd-8ec3-e3eb5160234f}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:26:56.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{a3735f0e-cec8-4fa6-91ef-111dcc74cf12}" done="0">
     <x18tc:text xml:space="preserve">too complicated</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1762,79 +1762,79 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E59" dT="2026-03-14T21:09:28.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{c95b624b-6094-4cd0-9e1a-1db76a955c5c}" done="0">
+  <x18tc:threadedComment ref="E59" dT="2026-03-14T21:09:28.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{011fd032-94f4-4833-967f-304817de3267}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E25" dT="2026-03-14T20:30:47.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{51bacf10-e5fa-4c58-9333-c0b6dae0805d}" done="0">
+  <x18tc:threadedComment ref="E25" dT="2026-03-14T20:30:47.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{daa26dd0-ec64-4846-ab9c-83cae74a5d36}" done="0">
     <x18tc:text xml:space="preserve">ip address</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E22" dT="2026-03-14T20:29:38.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{7adfe208-3130-44a0-9f4d-0fb1c1850458}" done="0">
+  <x18tc:threadedComment ref="E22" dT="2026-03-14T20:29:38.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{3495ca3d-131a-4d92-8e4a-f39d30d48d39}" done="0">
     <x18tc:text xml:space="preserve">filtered notif</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E57" dT="2026-03-14T21:09:06.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{b9c7f014-dda7-4924-a30e-6ea6ff1fc5da}" done="0">
+  <x18tc:threadedComment ref="E57" dT="2026-03-14T21:09:06.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{3bcbe15d-7181-4d69-82b7-b54610d3c1ae}" done="0">
     <x18tc:text xml:space="preserve">to be reviewed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-03-14T20:30:29.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{5e39a9bf-5952-456e-8041-c356b89ea94c}" done="0">
+  <x18tc:threadedComment ref="E24" dT="2026-03-14T20:30:29.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{b54dbb6b-1a8b-4105-a84d-36b5794aa5de}" done="0">
     <x18tc:text xml:space="preserve">bulk import</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E98" dT="2026-03-14T21:14:01.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{8b7d8015-ed46-406d-9378-3c8634596926}" done="0">
+  <x18tc:threadedComment ref="E98" dT="2026-03-14T21:14:01.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{32eada8a-3806-4748-abd4-edd0714f7be0}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E37" dT="2026-03-14T21:06:29.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{28fb4e7d-cb5d-4d77-88d0-d51383682362}" done="0">
+  <x18tc:threadedComment ref="E36" dT="2026-03-14T21:06:29.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{191a5d8b-da35-46af-b884-e11080df99bc}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E95" dT="2026-03-14T21:13:30.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{f242f38a-e7fc-4a6f-ba2d-dd49ee03404c}" done="0">
+  <x18tc:threadedComment ref="E95" dT="2026-03-14T21:13:30.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{796f1b4b-3dec-4fca-a1c0-a91ad83df44f}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E97" dT="2026-03-14T21:13:49.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{fddd98d9-35f0-42e9-8589-424099660817}" done="0">
+  <x18tc:threadedComment ref="E97" dT="2026-03-14T21:13:49.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{34474ebd-51a2-4bd6-b5e7-e05f3b571e27}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E94" dT="2026-03-14T21:13:21.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{3984996c-de65-4413-8f8b-7c1943327248}" done="0">
+  <x18tc:threadedComment ref="E94" dT="2026-03-14T21:13:21.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E58" dT="2026-03-14T21:24:29.00" personId="{51111f04-29c5-459d-8381-a95c748291fc}" id="{5793895e-b99f-4827-bb5d-27a99d333e5d}" done="0">
+  <x18tc:threadedComment ref="E58" dT="2026-03-14T21:24:29.00" personId="{dd935650-9495-4a16-a7ad-a553b6027719}" id="{e0b710dc-ddc9-420a-89a0-f58422177788}" done="0">
     <x18tc:text xml:space="preserve">aaaaa</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E96" dT="2026-03-14T21:13:39.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{9a5a8381-0b2f-435c-8e7f-da7b8bdf0452}" done="0">
+  <x18tc:threadedComment ref="E96" dT="2026-03-14T21:13:39.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{0ca4a076-72d1-46fc-94b1-adc0329cd557}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E91" dT="2026-03-14T21:13:05.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{b82034be-dc46-4b4c-b506-6e738b06070e}" done="0">
+  <x18tc:threadedComment ref="E91" dT="2026-03-14T21:13:05.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{367ac776-ff23-4107-a3da-66a734b6359d}" done="0">
     <x18tc:text xml:space="preserve">combine 87,88,89</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E60" dT="2026-03-14T21:09:58.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{3aceb880-1b08-4db1-a1ac-4ea4b1bcc470}" done="0">
+  <x18tc:threadedComment ref="E60" dT="2026-03-14T21:09:58.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eae5a438-f943-4aac-8104-2d5447116caf}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E102" dT="2026-03-14T21:14:23.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{50624453-ed97-40cc-91fc-3d25638dc6b9}" done="0">
+  <x18tc:threadedComment ref="E102" dT="2026-03-14T21:14:23.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E87" dT="2026-03-14T21:12:31.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{f662b67a-6c34-4760-8f44-1e7efb7cbba7}" done="0">
+  <x18tc:threadedComment ref="E87" dT="2026-03-14T21:12:31.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{18863187-a8de-455d-9379-060c04b24aad}" done="0">
     <x18tc:text xml:space="preserve">UI</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E101" dT="2026-03-14T21:14:18.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{97eb5bb9-d623-4ac2-9140-5cba7448b912}" done="0">
+  <x18tc:threadedComment ref="E101" dT="2026-03-14T21:14:18.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eaf9c939-f963-4570-be66-42717b46b409}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E79" dT="2026-03-14T21:11:47.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{2530cb90-77d0-4225-8b87-5549bead3c80}" done="0">
+  <x18tc:threadedComment ref="E79" dT="2026-03-14T21:11:47.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{5e904548-7fec-4891-b6f5-23d22093d3f6}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E100" dT="2026-03-14T21:14:12.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{373c0738-96a6-48cf-b5f4-31dea957134a}" done="0">
+  <x18tc:threadedComment ref="E100" dT="2026-03-14T21:14:12.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{f5c155c2-d59b-4500-b951-4f3555a635ee}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E76" dT="2026-03-14T21:11:27.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{6c2f1a4d-5692-469c-93cf-2bd99f113aec}" done="0">
+  <x18tc:threadedComment ref="E76" dT="2026-03-14T21:11:27.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{e50642f5-662b-492e-8317-3e200d3d3550}" done="0">
     <x18tc:text xml:space="preserve">wrong</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E99" dT="2026-03-14T21:14:07.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{7ef3d4c1-a29c-4a4c-9d80-3306b1e9bcb5}" done="0">
+  <x18tc:threadedComment ref="E99" dT="2026-03-14T21:14:07.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{6e877e43-b507-481e-8b91-012db4e74917}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E36" dT="2026-03-14T21:06:09.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{8141c568-121a-4ec9-a95d-8e2100da1cec}" done="0">
+  <x18tc:threadedComment ref="E37" dT="2026-03-14T21:06:09.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{68a5be20-8c63-4013-b0e5-c37a35a49cc2}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E32" dT="2026-03-14T21:05:06.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{00754f08-030c-443a-96b7-1f90b44c035c}" done="0">
+  <x18tc:threadedComment ref="E32" dT="2026-03-14T21:05:06.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{260b74e2-c79b-4313-9bbe-dc58d0bd867f}" done="0">
     <x18tc:text xml:space="preserve">check</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E74" dT="2026-03-14T20:32:20.00" personId="{51111f04-29c5-459d-8381-a95c748291fc}" id="{180e5f80-0f99-465d-aeb8-5f33b703a8da}" done="0">
+  <x18tc:threadedComment ref="E74" dT="2026-03-14T20:32:20.00" personId="{dd935650-9495-4a16-a7ad-a553b6027719}" id="{55e228b8-6949-499c-a454-81f0501833b3}" done="0">
     <x18tc:text xml:space="preserve">x</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E26" dT="2026-03-14T20:31:28.00" personId="{07c35965-c11a-44ca-bfe5-3c6825f4a79a}" id="{87a67a64-e46a-4f8e-bfec-7d7aed281e71}" done="0">
+  <x18tc:threadedComment ref="E26" dT="2026-03-14T20:31:28.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{883914c5-7ce1-44b0-992a-c2d83e3b1a81}" done="0">
     <x18tc:text xml:space="preserve">will delete</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -3228,13 +3228,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="18.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="15.0"/>
-    <col customWidth="1" min="4" max="4" width="42.0"/>
-    <col customWidth="1" min="5" max="5" width="76.57"/>
-    <col customWidth="1" min="6" max="6" width="114.71"/>
-    <col customWidth="1" min="7" max="7" width="176.29"/>
+    <col customWidth="1" min="1" max="1" width="14.57"/>
+    <col customWidth="1" min="2" max="2" width="23.43"/>
+    <col customWidth="1" min="3" max="3" width="14.86"/>
+    <col customWidth="1" min="4" max="4" width="35.14"/>
+    <col customWidth="1" min="5" max="5" width="88.29"/>
+    <col customWidth="1" min="6" max="6" width="113.14"/>
+    <col customWidth="1" min="7" max="7" width="159.29"/>
     <col customWidth="1" min="8" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -3983,47 +3983,47 @@
       <c r="A36" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B36" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="21">
         <v>34.0</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="F36" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="G36" s="14"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="22">
         <v>35.0</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="G37" s="14"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="23" t="s">
         <v>125</v>
-      </c>
-      <c r="G37" s="16"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="21" t="s">
-        <v>126</v>
       </c>
       <c r="B38" s="14" t="s">
         <v>53</v>
@@ -4032,7 +4032,7 @@
         <v>36.0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>127</v>
@@ -4043,8 +4043,8 @@
       <c r="G38" s="14"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21" t="s">
-        <v>126</v>
+      <c r="A39" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>53</v>
@@ -4064,8 +4064,8 @@
       <c r="G39" s="16"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="21" t="s">
-        <v>126</v>
+      <c r="A40" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B40" s="14" t="s">
         <v>53</v>
@@ -4085,8 +4085,8 @@
       <c r="G40" s="14"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="21" t="s">
-        <v>126</v>
+      <c r="A41" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>133</v>
@@ -4095,7 +4095,7 @@
         <v>39.0</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E41" s="17" t="s">
         <v>134</v>
@@ -4106,8 +4106,8 @@
       <c r="G41" s="16"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="21" t="s">
-        <v>126</v>
+      <c r="A42" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>136</v>
@@ -4127,8 +4127,8 @@
       <c r="G42" s="14"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="21" t="s">
-        <v>126</v>
+      <c r="A43" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>139</v>
@@ -4137,7 +4137,7 @@
         <v>41.0</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E43" s="17" t="s">
         <v>140</v>
@@ -4148,8 +4148,8 @@
       <c r="G43" s="16"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="21" t="s">
-        <v>126</v>
+      <c r="A44" s="23" t="s">
+        <v>125</v>
       </c>
       <c r="B44" s="14" t="s">
         <v>139</v>
@@ -4158,7 +4158,7 @@
         <v>42.0</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>142</v>
@@ -4169,7 +4169,7 @@
       <c r="G44" s="14"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="22" t="s">
+      <c r="A45" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B45" s="16" t="s">
@@ -4179,7 +4179,7 @@
         <v>43.0</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E45" s="17" t="s">
         <v>146</v>
@@ -4192,7 +4192,7 @@
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B46" s="14" t="s">
@@ -4202,7 +4202,7 @@
         <v>44.0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>150</v>
@@ -4213,7 +4213,7 @@
       <c r="G46" s="14"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B47" s="16" t="s">
@@ -4223,7 +4223,7 @@
         <v>45.0</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E47" s="17" t="s">
         <v>153</v>
@@ -4236,7 +4236,7 @@
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="22" t="s">
+      <c r="A48" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B48" s="14" t="s">
@@ -4246,7 +4246,7 @@
         <v>46.0</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>157</v>
@@ -4257,7 +4257,7 @@
       <c r="G48" s="14"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="22" t="s">
+      <c r="A49" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B49" s="16" t="s">
@@ -4267,7 +4267,7 @@
         <v>47.0</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E49" s="17" t="s">
         <v>159</v>
@@ -4278,7 +4278,7 @@
       <c r="G49" s="16"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="22" t="s">
+      <c r="A50" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B50" s="14" t="s">
@@ -4288,7 +4288,7 @@
         <v>48.0</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E50" s="15" t="s">
         <v>161</v>
@@ -4301,7 +4301,7 @@
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B51" s="16" t="s">
@@ -4311,7 +4311,7 @@
         <v>49.0</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E51" s="17" t="s">
         <v>165</v>
@@ -4324,7 +4324,7 @@
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="22" t="s">
+      <c r="A52" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B52" s="14" t="s">
@@ -4334,7 +4334,7 @@
         <v>50.0</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E52" s="15" t="s">
         <v>169</v>
@@ -4345,7 +4345,7 @@
       <c r="G52" s="14"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="22" t="s">
+      <c r="A53" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B53" s="16" t="s">
@@ -4355,7 +4355,7 @@
         <v>51.0</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E53" s="17" t="s">
         <v>172</v>
@@ -4366,7 +4366,7 @@
       <c r="G53" s="16"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="22" t="s">
+      <c r="A54" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B54" s="14" t="s">
@@ -4376,7 +4376,7 @@
         <v>52.0</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>174</v>
@@ -4387,7 +4387,7 @@
       <c r="G54" s="14"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B55" s="16" t="s">
@@ -4408,7 +4408,7 @@
       <c r="G55" s="16"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="22" t="s">
+      <c r="A56" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B56" s="14" t="s">
@@ -4418,7 +4418,7 @@
         <v>54.0</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>179</v>
@@ -4429,7 +4429,7 @@
       <c r="G56" s="14"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B57" s="16" t="s">
@@ -4450,7 +4450,7 @@
       <c r="G57" s="16"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B58" s="14" t="s">
@@ -4460,7 +4460,7 @@
         <v>56.0</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>184</v>
@@ -4471,17 +4471,17 @@
       <c r="G58" s="14"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="22" t="s">
+      <c r="A59" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="21">
         <v>43.0</v>
       </c>
       <c r="C59" s="16">
         <v>57.0</v>
       </c>
-      <c r="D59" s="23" t="s">
-        <v>121</v>
+      <c r="D59" s="21" t="s">
+        <v>126</v>
       </c>
       <c r="E59" s="20" t="s">
         <v>186</v>
@@ -4492,17 +4492,17 @@
       <c r="G59" s="16"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="22" t="s">
+      <c r="A60" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B60" s="22">
         <v>43.0</v>
       </c>
       <c r="C60" s="14">
         <v>58.0</v>
       </c>
-      <c r="D60" s="24" t="s">
-        <v>121</v>
+      <c r="D60" s="22" t="s">
+        <v>126</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>188</v>
@@ -4546,7 +4546,7 @@
         <v>60.0</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>195</v>
@@ -4630,7 +4630,7 @@
         <v>64.0</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>203</v>
@@ -4800,7 +4800,7 @@
         <v>72.0</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E74" s="15" t="s">
         <v>224</v>
@@ -4863,7 +4863,7 @@
         <v>75.0</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E77" s="17" t="s">
         <v>232</v>
@@ -4884,7 +4884,7 @@
         <v>76.0</v>
       </c>
       <c r="D78" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E78" s="15" t="s">
         <v>235</v>
@@ -4993,7 +4993,7 @@
         <v>81.0</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E83" s="17" t="s">
         <v>251</v>
@@ -5035,7 +5035,7 @@
         <v>83.0</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E85" s="17" t="s">
         <v>256</v>
@@ -5098,7 +5098,7 @@
         <v>86.0</v>
       </c>
       <c r="D88" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E88" s="15" t="s">
         <v>263</v>
@@ -5140,7 +5140,7 @@
         <v>88.0</v>
       </c>
       <c r="D90" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E90" s="15" t="s">
         <v>268</v>
@@ -5161,7 +5161,7 @@
         <v>89.0</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E91" s="17" t="s">
         <v>271</v>
@@ -5182,7 +5182,7 @@
         <v>90.0</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E92" s="15" t="s">
         <v>273</v>
@@ -5203,7 +5203,7 @@
         <v>91.0</v>
       </c>
       <c r="D93" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E93" s="17" t="s">
         <v>275</v>
@@ -5224,7 +5224,7 @@
         <v>92.0</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E94" s="19" t="s">
         <v>277</v>
@@ -5244,8 +5244,8 @@
       <c r="C95" s="16">
         <v>93.0</v>
       </c>
-      <c r="D95" s="16" t="s">
-        <v>121</v>
+      <c r="D95" s="21" t="s">
+        <v>118</v>
       </c>
       <c r="E95" s="20" t="s">
         <v>279</v>
@@ -5287,7 +5287,7 @@
         <v>95.0</v>
       </c>
       <c r="D97" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E97" s="17" t="s">
         <v>285</v>
@@ -5392,7 +5392,7 @@
         <v>100.0</v>
       </c>
       <c r="D102" s="16" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E102" s="17" t="s">
         <v>297</v>
@@ -6316,11 +6316,11 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.0"/>
-    <col customWidth="1" min="2" max="2" width="30.57"/>
-    <col customWidth="1" min="3" max="3" width="70.0"/>
-    <col customWidth="1" min="4" max="4" width="50.0"/>
-    <col customWidth="1" min="5" max="5" width="40.0"/>
+    <col customWidth="1" min="1" max="1" width="14.86"/>
+    <col customWidth="1" min="2" max="2" width="26.43"/>
+    <col customWidth="1" min="3" max="3" width="70.14"/>
+    <col customWidth="1" min="4" max="4" width="49.43"/>
+    <col customWidth="1" min="5" max="5" width="36.57"/>
     <col customWidth="1" min="6" max="26" width="8.71"/>
   </cols>
   <sheetData>
@@ -6342,7 +6342,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24">
+      <c r="A2" s="22">
         <f t="shared" ref="A2:A11" si="1">ROW()-1</f>
         <v>1</v>
       </c>
@@ -6360,7 +6360,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24">
+      <c r="A3" s="22">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
@@ -6378,7 +6378,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24">
+      <c r="A4" s="22">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -6396,7 +6396,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24">
+      <c r="A5" s="22">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -6414,7 +6414,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24">
+      <c r="A6" s="22">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -6432,7 +6432,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24">
+      <c r="A7" s="22">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -6450,7 +6450,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24">
+      <c r="A8" s="22">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -6468,7 +6468,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24">
+      <c r="A9" s="22">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -6486,7 +6486,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24">
+      <c r="A10" s="22">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -6504,7 +6504,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24">
+      <c r="A11" s="22">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>

--- a/fianl.xlsx
+++ b/fianl.xlsx
@@ -15,11 +15,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={63d52799-d727-43cd-be68-dcd7fde7e657}</author>
-    <author>tc={a3735f0e-cec8-4fa6-91ef-111dcc74cf12}</author>
+    <author>tc={3f8dc711-f211-4e91-8afb-8611c2315205}</author>
+    <author>tc={bb7353cb-e82f-4ff6-9761-8cc67d16db56}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{63d52799-d727-43cd-be68-dcd7fde7e657}" ref="A1">
+    <comment authorId="0" xr:uid="{3f8dc711-f211-4e91-8afb-8611c2315205}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -28,7 +28,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{a3735f0e-cec8-4fa6-91ef-111dcc74cf12}" ref="A1">
+    <comment authorId="1" xr:uid="{bb7353cb-e82f-4ff6-9761-8cc67d16db56}" ref="A1">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -44,34 +44,160 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={011fd032-94f4-4833-967f-304817de3267}</author>
-    <author>tc={0ca4a076-72d1-46fc-94b1-adc0329cd557}</author>
-    <author>tc={18863187-a8de-455d-9379-060c04b24aad}</author>
-    <author>tc={191a5d8b-da35-46af-b884-e11080df99bc}</author>
-    <author>tc={1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}</author>
-    <author>tc={260b74e2-c79b-4313-9bbe-dc58d0bd867f}</author>
-    <author>tc={32eada8a-3806-4748-abd4-edd0714f7be0}</author>
-    <author>tc={34474ebd-51a2-4bd6-b5e7-e05f3b571e27}</author>
-    <author>tc={3495ca3d-131a-4d92-8e4a-f39d30d48d39}</author>
-    <author>tc={367ac776-ff23-4107-a3da-66a734b6359d}</author>
-    <author>tc={3bcbe15d-7181-4d69-82b7-b54610d3c1ae}</author>
-    <author>tc={55e228b8-6949-499c-a454-81f0501833b3}</author>
-    <author>tc={5e904548-7fec-4891-b6f5-23d22093d3f6}</author>
-    <author>tc={68a5be20-8c63-4013-b0e5-c37a35a49cc2}</author>
-    <author>tc={6e877e43-b507-481e-8b91-012db4e74917}</author>
-    <author>tc={796f1b4b-3dec-4fca-a1c0-a91ad83df44f}</author>
-    <author>tc={883914c5-7ce1-44b0-992a-c2d83e3b1a81}</author>
-    <author>tc={b54dbb6b-1a8b-4105-a84d-36b5794aa5de}</author>
-    <author>tc={daa26dd0-ec64-4846-ab9c-83cae74a5d36}</author>
-    <author>tc={e0b710dc-ddc9-420a-89a0-f58422177788}</author>
-    <author>tc={e50642f5-662b-492e-8317-3e200d3d3550}</author>
-    <author>tc={eae5a438-f943-4aac-8104-2d5447116caf}</author>
-    <author>tc={eaf9c939-f963-4570-be66-42717b46b409}</author>
-    <author>tc={eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}</author>
-    <author>tc={f5c155c2-d59b-4500-b951-4f3555a635ee}</author>
+    <author>tc={02300538-aae3-49dc-b25f-0b76aeb30f1e}</author>
+    <author>tc={0aa53cee-abb0-4cb8-9132-e72e741e7364}</author>
+    <author>tc={0df49c4f-d854-4ac0-82e8-40d2d7188874}</author>
+    <author>tc={18e1e645-492a-4576-8bcf-8a428d2b40ba}</author>
+    <author>tc={1c4d2b2b-8001-4321-a0ff-49de3872be48}</author>
+    <author>tc={2de44811-b8de-498d-b9e3-c54081118132}</author>
+    <author>tc={2ebfc623-76f0-4e67-9539-470fa64baffb}</author>
+    <author>tc={3edee14e-6ac8-48db-9c98-06e860772d63}</author>
+    <author>tc={4cd7f1c5-4012-4901-a166-b60b019df5e6}</author>
+    <author>tc={58fcb092-3d27-4ef3-ae2c-1d91d8efdcb1}</author>
+    <author>tc={5a1d720f-3827-4b31-aafa-378291acb158}</author>
+    <author>tc={5b22bf98-95df-480b-a127-ba4b3850e0d6}</author>
+    <author>tc={69dd9d0d-14e8-4a21-9308-ab73a34be44a}</author>
+    <author>tc={6df1b757-5c95-496b-bc46-91e00f46c2de}</author>
+    <author>tc={6f6e7479-79c4-4cb0-ade1-82374efc0d9a}</author>
+    <author>tc={7bb0aaa0-fd08-47cf-b52f-2fa984c4383a}</author>
+    <author>tc={80973caf-0d91-4bca-a789-3b977676890f}</author>
+    <author>tc={b7cc6900-b0fb-4562-9beb-508a46860c39}</author>
+    <author>tc={c0c7a83c-7074-445c-b2f3-b5c8a4026e9f}</author>
+    <author>tc={c15414b4-8535-4332-b4dd-21b0e0ef9848}</author>
+    <author>tc={c3d690a8-9c95-434e-9343-bddce899636b}</author>
+    <author>tc={dc9d1118-495e-44d2-bf4c-1da7701a5e04}</author>
+    <author>tc={e0afeec0-fd5d-4641-a720-efac846bee19}</author>
+    <author>tc={f7f4e609-60a8-4216-89b0-44c0b7b9fd13}</author>
+    <author>tc={fb9d092d-2086-4491-ba60-ad3eb2f0aa1f}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{011fd032-94f4-4833-967f-304817de3267}" ref="E59">
+    <comment authorId="0" xr:uid="{02300538-aae3-49dc-b25f-0b76aeb30f1e}" ref="E74">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	x
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{0aa53cee-abb0-4cb8-9132-e72e741e7364}" ref="E22">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	filtered notif
+</t>
+      </text>
+    </comment>
+    <comment authorId="2" xr:uid="{0df49c4f-d854-4ac0-82e8-40d2d7188874}" ref="E97">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="3" xr:uid="{18e1e645-492a-4576-8bcf-8a428d2b40ba}" ref="E36">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	WRONG!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="4" xr:uid="{1c4d2b2b-8001-4321-a0ff-49de3872be48}" ref="E96">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="5" xr:uid="{2de44811-b8de-498d-b9e3-c54081118132}" ref="E76">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong
+</t>
+      </text>
+    </comment>
+    <comment authorId="6" xr:uid="{2ebfc623-76f0-4e67-9539-470fa64baffb}" ref="E95">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="7" xr:uid="{3edee14e-6ac8-48db-9c98-06e860772d63}" ref="E58">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	aaaaa
+</t>
+      </text>
+    </comment>
+    <comment authorId="8" xr:uid="{4cd7f1c5-4012-4901-a166-b60b019df5e6}" ref="E37">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	WRONG!!
+</t>
+      </text>
+    </comment>
+    <comment authorId="9" xr:uid="{58fcb092-3d27-4ef3-ae2c-1d91d8efdcb1}" ref="E32">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	check
+</t>
+      </text>
+    </comment>
+    <comment authorId="10" xr:uid="{5a1d720f-3827-4b31-aafa-378291acb158}" ref="E57">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	to be reviewed
+</t>
+      </text>
+    </comment>
+    <comment authorId="11" xr:uid="{5b22bf98-95df-480b-a127-ba4b3850e0d6}" ref="E99">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!
+</t>
+      </text>
+    </comment>
+    <comment authorId="12" xr:uid="{69dd9d0d-14e8-4a21-9308-ab73a34be44a}" ref="E24">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	bulk import
+</t>
+      </text>
+    </comment>
+    <comment authorId="13" xr:uid="{6df1b757-5c95-496b-bc46-91e00f46c2de}" ref="E101">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	wrong!
+</t>
+      </text>
+    </comment>
+    <comment authorId="14" xr:uid="{6f6e7479-79c4-4cb0-ade1-82374efc0d9a}" ref="E59">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +206,34 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{0ca4a076-72d1-46fc-94b1-adc0329cd557}" ref="E96">
+    <comment authorId="15" xr:uid="{7bb0aaa0-fd08-47cf-b52f-2fa984c4383a}" ref="E87">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	UI
+</t>
+      </text>
+    </comment>
+    <comment authorId="16" xr:uid="{80973caf-0d91-4bca-a789-3b977676890f}" ref="E26">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	will delete
+</t>
+      </text>
+    </comment>
+    <comment authorId="17" xr:uid="{b7cc6900-b0fb-4562-9beb-508a46860c39}" ref="E25">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	ip address
+</t>
+      </text>
+    </comment>
+    <comment authorId="18" xr:uid="{c0c7a83c-7074-445c-b2f3-b5c8a4026e9f}" ref="E60">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,25 +242,34 @@
 </t>
       </text>
     </comment>
-    <comment authorId="2" xr:uid="{18863187-a8de-455d-9379-060c04b24aad}" ref="E87">
+    <comment authorId="19" xr:uid="{c15414b4-8535-4332-b4dd-21b0e0ef9848}" ref="E98">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	UI
+	wrong!!
 </t>
       </text>
     </comment>
-    <comment authorId="3" xr:uid="{191a5d8b-da35-46af-b884-e11080df99bc}" ref="E36">
+    <comment authorId="20" xr:uid="{c3d690a8-9c95-434e-9343-bddce899636b}" ref="E94">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-	WRONG!!
+	wrong!!
 </t>
       </text>
     </comment>
-    <comment authorId="4" xr:uid="{1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}" ref="E102">
+    <comment authorId="21" xr:uid="{dc9d1118-495e-44d2-bf4c-1da7701a5e04}" ref="E91">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	combine 87,88,89
+</t>
+      </text>
+    </comment>
+    <comment authorId="22" xr:uid="{e0afeec0-fd5d-4641-a720-efac846bee19}" ref="E102">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -116,88 +278,7 @@
 </t>
       </text>
     </comment>
-    <comment authorId="5" xr:uid="{260b74e2-c79b-4313-9bbe-dc58d0bd867f}" ref="E32">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	check
-</t>
-      </text>
-    </comment>
-    <comment authorId="6" xr:uid="{32eada8a-3806-4748-abd4-edd0714f7be0}" ref="E98">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="7" xr:uid="{34474ebd-51a2-4bd6-b5e7-e05f3b571e27}" ref="E97">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="8" xr:uid="{3495ca3d-131a-4d92-8e4a-f39d30d48d39}" ref="E22">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	filtered notif
-</t>
-      </text>
-    </comment>
-    <comment authorId="9" xr:uid="{367ac776-ff23-4107-a3da-66a734b6359d}" ref="E91">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	combine 87,88,89
-</t>
-      </text>
-    </comment>
-    <comment authorId="10" xr:uid="{3bcbe15d-7181-4d69-82b7-b54610d3c1ae}" ref="E57">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	to be reviewed
-</t>
-      </text>
-    </comment>
-    <comment authorId="11" xr:uid="{55e228b8-6949-499c-a454-81f0501833b3}" ref="E74">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	x
-</t>
-      </text>
-    </comment>
-    <comment authorId="12" xr:uid="{5e904548-7fec-4891-b6f5-23d22093d3f6}" ref="E79">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="13" xr:uid="{68a5be20-8c63-4013-b0e5-c37a35a49cc2}" ref="E37">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	WRONG!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="14" xr:uid="{6e877e43-b507-481e-8b91-012db4e74917}" ref="E99">
+    <comment authorId="23" xr:uid="{f7f4e609-60a8-4216-89b0-44c0b7b9fd13}" ref="E100">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -206,93 +287,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="15" xr:uid="{796f1b4b-3dec-4fca-a1c0-a91ad83df44f}" ref="E95">
+    <comment authorId="24" xr:uid="{fb9d092d-2086-4491-ba60-ad3eb2f0aa1f}" ref="E79">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
 	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="16" xr:uid="{883914c5-7ce1-44b0-992a-c2d83e3b1a81}" ref="E26">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	will delete
-</t>
-      </text>
-    </comment>
-    <comment authorId="17" xr:uid="{b54dbb6b-1a8b-4105-a84d-36b5794aa5de}" ref="E24">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	bulk import
-</t>
-      </text>
-    </comment>
-    <comment authorId="18" xr:uid="{daa26dd0-ec64-4846-ab9c-83cae74a5d36}" ref="E25">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	ip address
-</t>
-      </text>
-    </comment>
-    <comment authorId="19" xr:uid="{e0b710dc-ddc9-420a-89a0-f58422177788}" ref="E58">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	aaaaa
-</t>
-      </text>
-    </comment>
-    <comment authorId="20" xr:uid="{e50642f5-662b-492e-8317-3e200d3d3550}" ref="E76">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong
-</t>
-      </text>
-    </comment>
-    <comment authorId="21" xr:uid="{eae5a438-f943-4aac-8104-2d5447116caf}" ref="E60">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="22" xr:uid="{eaf9c939-f963-4570-be66-42717b46b409}" ref="E101">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!
-</t>
-      </text>
-    </comment>
-    <comment authorId="23" xr:uid="{eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}" ref="E94">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!!
-</t>
-      </text>
-    </comment>
-    <comment authorId="24" xr:uid="{f5c155c2-d59b-4500-b951-4f3555a635ee}" ref="E100">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	wrong!
 </t>
       </text>
     </comment>
@@ -336,7 +336,7 @@
     <t>T19</t>
   </si>
   <si>
-    <t>Basel Samer</t>
+    <t>Basel Samer Osman</t>
   </si>
   <si>
     <t>61-3780</t>
@@ -1451,7 +1451,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1494,6 +1494,9 @@
     <xf borderId="1" fillId="4" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1510,14 +1513,14 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1550,8 +1553,8 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="basel samer" id="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" providerId="google-sheets"/>
-  <x18tc:person displayName="Omar Ahmed" id="{dd935650-9495-4a16-a7ad-a553b6027719}" providerId="google-sheets"/>
+  <x18tc:person displayName="basel samer" id="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" providerId="google-sheets"/>
+  <x18tc:person displayName="Omar Ahmed" id="{223caded-4ff2-4de2-8324-f46feccd7b01}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1751,10 +1754,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:28:39.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{63d52799-d727-43cd-be68-dcd7fde7e657}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:28:39.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{3f8dc711-f211-4e91-8afb-8611c2315205}" done="0">
     <x18tc:text xml:space="preserve">complicated</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:26:56.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{a3735f0e-cec8-4fa6-91ef-111dcc74cf12}" done="0">
+  <x18tc:threadedComment ref="A1" dT="2026-03-14T21:26:56.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{bb7353cb-e82f-4ff6-9761-8cc67d16db56}" done="0">
     <x18tc:text xml:space="preserve">too complicated</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -1762,79 +1765,79 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="E59" dT="2026-03-14T21:09:28.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{011fd032-94f4-4833-967f-304817de3267}" done="0">
+  <x18tc:threadedComment ref="E59" dT="2026-03-14T21:09:28.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{6f6e7479-79c4-4cb0-ade1-82374efc0d9a}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E25" dT="2026-03-14T20:30:47.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{daa26dd0-ec64-4846-ab9c-83cae74a5d36}" done="0">
+  <x18tc:threadedComment ref="E25" dT="2026-03-14T20:30:47.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{b7cc6900-b0fb-4562-9beb-508a46860c39}" done="0">
     <x18tc:text xml:space="preserve">ip address</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E22" dT="2026-03-14T20:29:38.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{3495ca3d-131a-4d92-8e4a-f39d30d48d39}" done="0">
+  <x18tc:threadedComment ref="E22" dT="2026-03-14T20:29:38.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{0aa53cee-abb0-4cb8-9132-e72e741e7364}" done="0">
     <x18tc:text xml:space="preserve">filtered notif</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E57" dT="2026-03-14T21:09:06.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{3bcbe15d-7181-4d69-82b7-b54610d3c1ae}" done="0">
+  <x18tc:threadedComment ref="E57" dT="2026-03-14T21:09:06.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{5a1d720f-3827-4b31-aafa-378291acb158}" done="0">
     <x18tc:text xml:space="preserve">to be reviewed</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E24" dT="2026-03-14T20:30:29.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{b54dbb6b-1a8b-4105-a84d-36b5794aa5de}" done="0">
+  <x18tc:threadedComment ref="E24" dT="2026-03-14T20:30:29.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{69dd9d0d-14e8-4a21-9308-ab73a34be44a}" done="0">
     <x18tc:text xml:space="preserve">bulk import</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E98" dT="2026-03-14T21:14:01.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{32eada8a-3806-4748-abd4-edd0714f7be0}" done="0">
+  <x18tc:threadedComment ref="E98" dT="2026-03-14T21:14:01.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{c15414b4-8535-4332-b4dd-21b0e0ef9848}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E36" dT="2026-03-14T21:06:29.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{191a5d8b-da35-46af-b884-e11080df99bc}" done="0">
+  <x18tc:threadedComment ref="E36" dT="2026-03-14T21:06:29.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{18e1e645-492a-4576-8bcf-8a428d2b40ba}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E95" dT="2026-03-14T21:13:30.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{796f1b4b-3dec-4fca-a1c0-a91ad83df44f}" done="0">
+  <x18tc:threadedComment ref="E95" dT="2026-03-14T21:13:30.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{2ebfc623-76f0-4e67-9539-470fa64baffb}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E97" dT="2026-03-14T21:13:49.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{34474ebd-51a2-4bd6-b5e7-e05f3b571e27}" done="0">
+  <x18tc:threadedComment ref="E97" dT="2026-03-14T21:13:49.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{0df49c4f-d854-4ac0-82e8-40d2d7188874}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E94" dT="2026-03-14T21:13:21.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eb3f15f8-f415-4700-b8a9-934a4cd0ceb9}" done="0">
+  <x18tc:threadedComment ref="E94" dT="2026-03-14T21:13:21.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{c3d690a8-9c95-434e-9343-bddce899636b}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E58" dT="2026-03-14T21:24:29.00" personId="{dd935650-9495-4a16-a7ad-a553b6027719}" id="{e0b710dc-ddc9-420a-89a0-f58422177788}" done="0">
+  <x18tc:threadedComment ref="E58" dT="2026-03-14T21:24:29.00" personId="{223caded-4ff2-4de2-8324-f46feccd7b01}" id="{3edee14e-6ac8-48db-9c98-06e860772d63}" done="0">
     <x18tc:text xml:space="preserve">aaaaa</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E96" dT="2026-03-14T21:13:39.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{0ca4a076-72d1-46fc-94b1-adc0329cd557}" done="0">
+  <x18tc:threadedComment ref="E96" dT="2026-03-14T21:13:39.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{1c4d2b2b-8001-4321-a0ff-49de3872be48}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E91" dT="2026-03-14T21:13:05.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{367ac776-ff23-4107-a3da-66a734b6359d}" done="0">
+  <x18tc:threadedComment ref="E91" dT="2026-03-14T21:13:05.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{dc9d1118-495e-44d2-bf4c-1da7701a5e04}" done="0">
     <x18tc:text xml:space="preserve">combine 87,88,89</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E60" dT="2026-03-14T21:09:58.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eae5a438-f943-4aac-8104-2d5447116caf}" done="0">
+  <x18tc:threadedComment ref="E60" dT="2026-03-14T21:09:58.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{c0c7a83c-7074-445c-b2f3-b5c8a4026e9f}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E102" dT="2026-03-14T21:14:23.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{1c4e0437-e027-4c1d-9b82-2d1c09a1b6dc}" done="0">
+  <x18tc:threadedComment ref="E102" dT="2026-03-14T21:14:23.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{e0afeec0-fd5d-4641-a720-efac846bee19}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E87" dT="2026-03-14T21:12:31.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{18863187-a8de-455d-9379-060c04b24aad}" done="0">
+  <x18tc:threadedComment ref="E87" dT="2026-03-14T21:12:31.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{7bb0aaa0-fd08-47cf-b52f-2fa984c4383a}" done="0">
     <x18tc:text xml:space="preserve">UI</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E101" dT="2026-03-14T21:14:18.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{eaf9c939-f963-4570-be66-42717b46b409}" done="0">
+  <x18tc:threadedComment ref="E101" dT="2026-03-14T21:14:18.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{6df1b757-5c95-496b-bc46-91e00f46c2de}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E79" dT="2026-03-14T21:11:47.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{5e904548-7fec-4891-b6f5-23d22093d3f6}" done="0">
+  <x18tc:threadedComment ref="E79" dT="2026-03-14T21:11:47.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{fb9d092d-2086-4491-ba60-ad3eb2f0aa1f}" done="0">
     <x18tc:text xml:space="preserve">wrong!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E100" dT="2026-03-14T21:14:12.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{f5c155c2-d59b-4500-b951-4f3555a635ee}" done="0">
+  <x18tc:threadedComment ref="E100" dT="2026-03-14T21:14:12.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{f7f4e609-60a8-4216-89b0-44c0b7b9fd13}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E76" dT="2026-03-14T21:11:27.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{e50642f5-662b-492e-8317-3e200d3d3550}" done="0">
+  <x18tc:threadedComment ref="E76" dT="2026-03-14T21:11:27.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{2de44811-b8de-498d-b9e3-c54081118132}" done="0">
     <x18tc:text xml:space="preserve">wrong</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E99" dT="2026-03-14T21:14:07.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{6e877e43-b507-481e-8b91-012db4e74917}" done="0">
+  <x18tc:threadedComment ref="E99" dT="2026-03-14T21:14:07.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{5b22bf98-95df-480b-a127-ba4b3850e0d6}" done="0">
     <x18tc:text xml:space="preserve">wrong!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E37" dT="2026-03-14T21:06:09.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{68a5be20-8c63-4013-b0e5-c37a35a49cc2}" done="0">
+  <x18tc:threadedComment ref="E37" dT="2026-03-14T21:06:09.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{4cd7f1c5-4012-4901-a166-b60b019df5e6}" done="0">
     <x18tc:text xml:space="preserve">WRONG!!</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E32" dT="2026-03-14T21:05:06.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{260b74e2-c79b-4313-9bbe-dc58d0bd867f}" done="0">
+  <x18tc:threadedComment ref="E32" dT="2026-03-14T21:05:06.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{58fcb092-3d27-4ef3-ae2c-1d91d8efdcb1}" done="0">
     <x18tc:text xml:space="preserve">check</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E74" dT="2026-03-14T20:32:20.00" personId="{dd935650-9495-4a16-a7ad-a553b6027719}" id="{55e228b8-6949-499c-a454-81f0501833b3}" done="0">
+  <x18tc:threadedComment ref="E74" dT="2026-03-14T20:32:20.00" personId="{223caded-4ff2-4de2-8324-f46feccd7b01}" id="{02300538-aae3-49dc-b25f-0b76aeb30f1e}" done="0">
     <x18tc:text xml:space="preserve">x</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="E26" dT="2026-03-14T20:31:28.00" personId="{d9457b2b-d6c3-414a-a218-7572e2cd7efe}" id="{883914c5-7ce1-44b0-992a-c2d83e3b1a81}" done="0">
+  <x18tc:threadedComment ref="E26" dT="2026-03-14T20:31:28.00" personId="{9c5ca3cb-c272-4cbf-90a3-9524f5127caf}" id="{80973caf-0d91-4bca-a789-3b977676890f}" done="0">
     <x18tc:text xml:space="preserve">will delete</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -2056,7 +2059,7 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -3268,16 +3271,16 @@
       <c r="B2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="14">
-        <v>1.0</v>
+      <c r="C2" s="15">
+        <v>0.0</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G2" s="14"/>
@@ -3286,22 +3289,22 @@
       <c r="A3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="17">
         <v>1.0</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="16"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="s">
@@ -3316,10 +3319,10 @@
       <c r="D4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="16" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="14"/>
@@ -3328,22 +3331,22 @@
       <c r="A5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>3.0</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="16"/>
+      <c r="G5" s="17"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="s">
@@ -3358,10 +3361,10 @@
       <c r="D6" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="16" t="s">
         <v>43</v>
       </c>
       <c r="G6" s="14"/>
@@ -3370,22 +3373,22 @@
       <c r="A7" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <v>5.0</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G7" s="16"/>
+      <c r="G7" s="17"/>
     </row>
     <row r="8">
       <c r="A8" s="13" t="s">
@@ -3400,10 +3403,10 @@
       <c r="D8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="16" t="s">
         <v>51</v>
       </c>
       <c r="G8" s="14" t="s">
@@ -3414,22 +3417,22 @@
       <c r="A9" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <v>7.0</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G9" s="16"/>
+      <c r="G9" s="17"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="s">
@@ -3444,10 +3447,10 @@
       <c r="D10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>58</v>
       </c>
       <c r="G10" s="14"/>
@@ -3456,22 +3459,22 @@
       <c r="A11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <v>9.0</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="16"/>
+      <c r="G11" s="17"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="s">
@@ -3486,37 +3489,37 @@
       <c r="D12" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="16" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="14"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <v>11.0</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="G13" s="16"/>
+      <c r="G13" s="17"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="14" t="s">
@@ -3528,37 +3531,37 @@
       <c r="D14" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="16" t="s">
         <v>67</v>
       </c>
       <c r="G14" s="14"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <v>13.0</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="F15" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="16"/>
+      <c r="G15" s="17"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B16" s="14" t="s">
@@ -3570,37 +3573,37 @@
       <c r="D16" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="16" t="s">
         <v>73</v>
       </c>
       <c r="G16" s="14"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <v>15.0</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G17" s="16"/>
+      <c r="G17" s="17"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B18" s="14" t="s">
@@ -3612,37 +3615,37 @@
       <c r="D18" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="16" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="14"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <v>17.0</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="16"/>
+      <c r="G19" s="17"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="14" t="s">
@@ -3654,37 +3657,37 @@
       <c r="D20" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="16" t="s">
         <v>81</v>
       </c>
       <c r="G20" s="14"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <v>19.0</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="17" t="s">
+      <c r="F21" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="16"/>
+      <c r="G21" s="17"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -3696,37 +3699,37 @@
       <c r="D22" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="16" t="s">
         <v>85</v>
       </c>
       <c r="G22" s="14"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <v>21.0</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="17" t="s">
+      <c r="F23" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="G23" s="16"/>
+      <c r="G23" s="17"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -3738,37 +3741,37 @@
       <c r="D24" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="16" t="s">
         <v>89</v>
       </c>
       <c r="G24" s="14"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="17">
         <v>23.0</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G25" s="16"/>
+      <c r="G25" s="17"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B26" s="14" t="s">
@@ -3780,39 +3783,39 @@
       <c r="D26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="16" t="s">
         <v>93</v>
       </c>
       <c r="G26" s="14"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="17">
         <v>25.0</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="17" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B28" s="14" t="s">
@@ -3824,37 +3827,37 @@
       <c r="D28" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="16" t="s">
         <v>99</v>
       </c>
       <c r="G28" s="14"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="17">
         <v>27.0</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="16"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B30" s="14" t="s">
@@ -3866,37 +3869,37 @@
       <c r="D30" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="16" t="s">
         <v>105</v>
       </c>
       <c r="G30" s="14"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="17">
         <v>29.0</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="G31" s="16"/>
+      <c r="G31" s="17"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B32" s="14" t="s">
@@ -3908,37 +3911,37 @@
       <c r="D32" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="16" t="s">
         <v>110</v>
       </c>
       <c r="G32" s="14"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="17">
         <v>31.0</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D33" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="G33" s="16"/>
+      <c r="G33" s="17"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B34" s="14" t="s">
@@ -3950,73 +3953,73 @@
       <c r="D34" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>116</v>
       </c>
       <c r="G34" s="14"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="17">
         <v>33.0</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="16"/>
+      <c r="G35" s="17"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="21">
+      <c r="C36" s="22">
         <v>34.0</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="G36" s="16"/>
+      <c r="G36" s="17"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="19" t="s">
         <v>63</v>
       </c>
       <c r="B37" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C37" s="22">
+      <c r="C37" s="15">
         <v>35.0</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="E37" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="20" t="s">
         <v>124</v>
       </c>
       <c r="G37" s="14"/>
@@ -4034,10 +4037,10 @@
       <c r="D38" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="16" t="s">
         <v>128</v>
       </c>
       <c r="G38" s="14"/>
@@ -4046,22 +4049,22 @@
       <c r="A39" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <v>37.0</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="G39" s="16"/>
+      <c r="G39" s="17"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="23" t="s">
@@ -4076,10 +4079,10 @@
       <c r="D40" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="16" t="s">
         <v>132</v>
       </c>
       <c r="G40" s="14"/>
@@ -4088,22 +4091,22 @@
       <c r="A41" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="17">
         <v>39.0</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="G41" s="16"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="23" t="s">
@@ -4118,10 +4121,10 @@
       <c r="D42" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="16" t="s">
         <v>138</v>
       </c>
       <c r="G42" s="14"/>
@@ -4130,22 +4133,22 @@
       <c r="A43" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="17">
         <v>41.0</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="G43" s="16"/>
+      <c r="G43" s="17"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="23" t="s">
@@ -4160,10 +4163,10 @@
       <c r="D44" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="16" t="s">
         <v>143</v>
       </c>
       <c r="G44" s="14"/>
@@ -4172,22 +4175,22 @@
       <c r="A45" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="17">
         <v>43.0</v>
       </c>
-      <c r="D45" s="16" t="s">
+      <c r="D45" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="F45" s="17" t="s">
+      <c r="F45" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="17" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4204,10 +4207,10 @@
       <c r="D46" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="16" t="s">
         <v>151</v>
       </c>
       <c r="G46" s="14"/>
@@ -4216,22 +4219,22 @@
       <c r="A47" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="17">
         <v>45.0</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="G47" s="16" t="s">
+      <c r="G47" s="17" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4248,10 +4251,10 @@
       <c r="D48" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="16" t="s">
         <v>158</v>
       </c>
       <c r="G48" s="14"/>
@@ -4260,22 +4263,22 @@
       <c r="A49" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="17">
         <v>47.0</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="G49" s="16"/>
+      <c r="G49" s="17"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="24" t="s">
@@ -4290,10 +4293,10 @@
       <c r="D50" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="16" t="s">
         <v>162</v>
       </c>
       <c r="G50" s="14" t="s">
@@ -4304,22 +4307,22 @@
       <c r="A51" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B51" s="16" t="s">
+      <c r="B51" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="17">
         <v>49.0</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="17" t="s">
         <v>167</v>
       </c>
     </row>
@@ -4336,10 +4339,10 @@
       <c r="D52" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F52" s="15" t="s">
+      <c r="F52" s="16" t="s">
         <v>170</v>
       </c>
       <c r="G52" s="14"/>
@@ -4348,22 +4351,22 @@
       <c r="A53" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B53" s="16" t="s">
+      <c r="B53" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="17">
         <v>51.0</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F53" s="17" t="s">
+      <c r="F53" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="G53" s="16"/>
+      <c r="G53" s="17"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="24" t="s">
@@ -4378,10 +4381,10 @@
       <c r="D54" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="16" t="s">
         <v>175</v>
       </c>
       <c r="G54" s="14"/>
@@ -4390,22 +4393,22 @@
       <c r="A55" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="17">
         <v>53.0</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="F55" s="17" t="s">
+      <c r="F55" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G55" s="16"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="24" t="s">
@@ -4420,10 +4423,10 @@
       <c r="D56" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E56" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="F56" s="15" t="s">
+      <c r="F56" s="16" t="s">
         <v>180</v>
       </c>
       <c r="G56" s="14"/>
@@ -4432,22 +4435,22 @@
       <c r="A57" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B57" s="16" t="s">
+      <c r="B57" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="16">
+      <c r="C57" s="17">
         <v>55.0</v>
       </c>
-      <c r="D57" s="16" t="s">
+      <c r="D57" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="F57" s="17" t="s">
+      <c r="F57" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="G57" s="16"/>
+      <c r="G57" s="17"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="24" t="s">
@@ -4462,10 +4465,10 @@
       <c r="D58" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E58" s="19" t="s">
+      <c r="E58" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="F58" s="19" t="s">
+      <c r="F58" s="20" t="s">
         <v>185</v>
       </c>
       <c r="G58" s="14"/>
@@ -4474,64 +4477,64 @@
       <c r="A59" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="25">
         <v>43.0</v>
       </c>
-      <c r="C59" s="16">
+      <c r="C59" s="17">
         <v>57.0</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="G59" s="16"/>
+      <c r="G59" s="17"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B60" s="22">
+      <c r="B60" s="26">
         <v>43.0</v>
       </c>
       <c r="C60" s="14">
         <v>58.0</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="E60" s="19" t="s">
+      <c r="E60" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="F60" s="19" t="s">
+      <c r="F60" s="20" t="s">
         <v>189</v>
       </c>
       <c r="G60" s="14"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="16" t="s">
+      <c r="A61" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C61" s="16">
+      <c r="C61" s="17">
         <v>59.0</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="F61" s="17" t="s">
+      <c r="F61" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="G61" s="16" t="s">
+      <c r="G61" s="17" t="s">
         <v>193</v>
       </c>
     </row>
@@ -4548,34 +4551,34 @@
       <c r="D62" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E62" s="15" t="s">
+      <c r="E62" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F62" s="15" t="s">
+      <c r="F62" s="16" t="s">
         <v>196</v>
       </c>
       <c r="G62" s="14"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B63" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C63" s="16">
+      <c r="C63" s="17">
         <v>61.0</v>
       </c>
-      <c r="D63" s="16" t="s">
+      <c r="D63" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="F63" s="17" t="s">
+      <c r="F63" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="G63" s="16"/>
+      <c r="G63" s="17"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="14" t="s">
@@ -4590,34 +4593,34 @@
       <c r="D64" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E64" s="15" t="s">
+      <c r="E64" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="F64" s="15" t="s">
+      <c r="F64" s="16" t="s">
         <v>200</v>
       </c>
       <c r="G64" s="14"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="16">
+      <c r="C65" s="17">
         <v>63.0</v>
       </c>
-      <c r="D65" s="16" t="s">
+      <c r="D65" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="F65" s="17" t="s">
+      <c r="F65" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="G65" s="16"/>
+      <c r="G65" s="17"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="14" t="s">
@@ -4632,34 +4635,34 @@
       <c r="D66" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E66" s="15" t="s">
+      <c r="E66" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="F66" s="15" t="s">
+      <c r="F66" s="16" t="s">
         <v>204</v>
       </c>
       <c r="G66" s="14"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C67" s="16">
+      <c r="C67" s="17">
         <v>65.0</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="F67" s="17" t="s">
+      <c r="F67" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="G67" s="16"/>
+      <c r="G67" s="17"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="14" t="s">
@@ -4674,34 +4677,34 @@
       <c r="D68" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E68" s="15" t="s">
+      <c r="E68" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F68" s="15" t="s">
+      <c r="F68" s="16" t="s">
         <v>208</v>
       </c>
       <c r="G68" s="14"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B69" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="C69" s="16">
+      <c r="C69" s="17">
         <v>67.0</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F69" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="G69" s="16" t="s">
+      <c r="G69" s="17" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4718,34 +4721,34 @@
       <c r="D70" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E70" s="15" t="s">
+      <c r="E70" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="F70" s="15" t="s">
+      <c r="F70" s="16" t="s">
         <v>215</v>
       </c>
       <c r="G70" s="14"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="16" t="s">
+      <c r="A71" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B71" s="16" t="s">
+      <c r="B71" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C71" s="16">
+      <c r="C71" s="17">
         <v>69.0</v>
       </c>
-      <c r="D71" s="16" t="s">
+      <c r="D71" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="F71" s="17" t="s">
+      <c r="F71" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="G71" s="16"/>
+      <c r="G71" s="17"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="14" t="s">
@@ -4760,34 +4763,34 @@
       <c r="D72" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E72" s="15" t="s">
+      <c r="E72" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F72" s="16" t="s">
         <v>220</v>
       </c>
       <c r="G72" s="14"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B73" s="16" t="s">
+      <c r="B73" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="C73" s="16">
+      <c r="C73" s="17">
         <v>71.0</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="18" t="s">
         <v>222</v>
       </c>
-      <c r="F73" s="17" t="s">
+      <c r="F73" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="G73" s="16"/>
+      <c r="G73" s="17"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="14" t="s">
@@ -4802,34 +4805,34 @@
       <c r="D74" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E74" s="15" t="s">
+      <c r="E74" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F74" s="15" t="s">
+      <c r="F74" s="16" t="s">
         <v>225</v>
       </c>
       <c r="G74" s="14"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B75" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C75" s="16">
+      <c r="C75" s="17">
         <v>73.0</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D75" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F75" s="17" t="s">
+      <c r="F75" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="G75" s="16"/>
+      <c r="G75" s="17"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="14" t="s">
@@ -4844,34 +4847,34 @@
       <c r="D76" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E76" s="15" t="s">
+      <c r="E76" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F76" s="15" t="s">
+      <c r="F76" s="16" t="s">
         <v>231</v>
       </c>
       <c r="G76" s="14"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B77" s="16" t="s">
+      <c r="B77" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="C77" s="16">
+      <c r="C77" s="17">
         <v>75.0</v>
       </c>
-      <c r="D77" s="16" t="s">
+      <c r="D77" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="18" t="s">
         <v>232</v>
       </c>
-      <c r="F77" s="17" t="s">
+      <c r="F77" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="G77" s="16"/>
+      <c r="G77" s="17"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="14" t="s">
@@ -4886,34 +4889,34 @@
       <c r="D78" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E78" s="15" t="s">
+      <c r="E78" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="F78" s="15" t="s">
+      <c r="F78" s="16" t="s">
         <v>236</v>
       </c>
       <c r="G78" s="14"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="C79" s="16">
+      <c r="C79" s="17">
         <v>77.0</v>
       </c>
-      <c r="D79" s="16" t="s">
+      <c r="D79" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="F79" s="17" t="s">
+      <c r="F79" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="G79" s="16"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="14" t="s">
@@ -4928,10 +4931,10 @@
       <c r="D80" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="E80" s="15" t="s">
+      <c r="E80" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="F80" s="15" t="s">
+      <c r="F80" s="16" t="s">
         <v>241</v>
       </c>
       <c r="G80" s="14" t="s">
@@ -4939,25 +4942,25 @@
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C81" s="16">
+      <c r="C81" s="17">
         <v>79.0</v>
       </c>
-      <c r="D81" s="16" t="s">
+      <c r="D81" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="G81" s="16"/>
+      <c r="G81" s="17"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="14" t="s">
@@ -4972,10 +4975,10 @@
       <c r="D82" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E82" s="15" t="s">
+      <c r="E82" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="F82" s="15" t="s">
+      <c r="F82" s="16" t="s">
         <v>248</v>
       </c>
       <c r="G82" s="14" t="s">
@@ -4983,25 +4986,25 @@
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="C83" s="16">
+      <c r="C83" s="17">
         <v>81.0</v>
       </c>
-      <c r="D83" s="16" t="s">
+      <c r="D83" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="F83" s="17" t="s">
+      <c r="F83" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="G83" s="16"/>
+      <c r="G83" s="17"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="14" t="s">
@@ -5016,34 +5019,34 @@
       <c r="D84" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E84" s="15" t="s">
+      <c r="E84" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="F84" s="15" t="s">
+      <c r="F84" s="16" t="s">
         <v>255</v>
       </c>
       <c r="G84" s="14"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="16" t="s">
+      <c r="A85" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B85" s="16" t="s">
+      <c r="B85" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C85" s="16">
+      <c r="C85" s="17">
         <v>83.0</v>
       </c>
-      <c r="D85" s="16" t="s">
+      <c r="D85" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="F85" s="17" t="s">
+      <c r="F85" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="G85" s="16"/>
+      <c r="G85" s="17"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="14" t="s">
@@ -5058,34 +5061,34 @@
       <c r="D86" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E86" s="15" t="s">
+      <c r="E86" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="16" t="s">
         <v>259</v>
       </c>
       <c r="G86" s="14"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="17" t="s">
         <v>246</v>
       </c>
       <c r="B87" s="25">
         <v>80.0</v>
       </c>
-      <c r="C87" s="16">
+      <c r="C87" s="17">
         <v>85.0</v>
       </c>
-      <c r="D87" s="16" t="s">
+      <c r="D87" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E87" s="20" t="s">
+      <c r="E87" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="F87" s="20" t="s">
+      <c r="F87" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="G87" s="16"/>
+      <c r="G87" s="17"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="14" t="s">
@@ -5100,34 +5103,34 @@
       <c r="D88" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F88" s="15" t="s">
+      <c r="F88" s="16" t="s">
         <v>264</v>
       </c>
       <c r="G88" s="14"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="C89" s="16">
+      <c r="C89" s="17">
         <v>87.0</v>
       </c>
-      <c r="D89" s="16" t="s">
+      <c r="D89" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="F89" s="17" t="s">
+      <c r="F89" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="G89" s="16"/>
+      <c r="G89" s="17"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="14" t="s">
@@ -5142,34 +5145,34 @@
       <c r="D90" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E90" s="15" t="s">
+      <c r="E90" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="F90" s="15" t="s">
+      <c r="F90" s="16" t="s">
         <v>269</v>
       </c>
       <c r="G90" s="14"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C91" s="16">
+      <c r="C91" s="17">
         <v>89.0</v>
       </c>
-      <c r="D91" s="16" t="s">
+      <c r="D91" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="F91" s="17" t="s">
+      <c r="F91" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="G91" s="16"/>
+      <c r="G91" s="17"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="14" t="s">
@@ -5184,34 +5187,34 @@
       <c r="D92" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E92" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="F92" s="15" t="s">
+      <c r="F92" s="16" t="s">
         <v>274</v>
       </c>
       <c r="G92" s="14"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B93" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C93" s="16">
+      <c r="C93" s="17">
         <v>91.0</v>
       </c>
-      <c r="D93" s="16" t="s">
+      <c r="D93" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="F93" s="17" t="s">
+      <c r="F93" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="G93" s="16"/>
+      <c r="G93" s="17"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="14" t="s">
@@ -5226,34 +5229,34 @@
       <c r="D94" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="E94" s="19" t="s">
+      <c r="E94" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="F94" s="19" t="s">
+      <c r="F94" s="20" t="s">
         <v>278</v>
       </c>
       <c r="G94" s="14"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="16" t="s">
+      <c r="A95" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B95" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C95" s="16">
+      <c r="C95" s="17">
         <v>93.0</v>
       </c>
-      <c r="D95" s="21" t="s">
+      <c r="D95" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="E95" s="20" t="s">
+      <c r="E95" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="F95" s="20" t="s">
+      <c r="F95" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="G95" s="16"/>
+      <c r="G95" s="17"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="14" t="s">
@@ -5268,34 +5271,34 @@
       <c r="D96" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E96" s="15" t="s">
+      <c r="E96" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="F96" s="15" t="s">
+      <c r="F96" s="16" t="s">
         <v>283</v>
       </c>
       <c r="G96" s="14"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B97" s="16" t="s">
+      <c r="B97" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="C97" s="16">
+      <c r="C97" s="17">
         <v>95.0</v>
       </c>
-      <c r="D97" s="16" t="s">
+      <c r="D97" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E97" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="F97" s="17" t="s">
+      <c r="F97" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="G97" s="16"/>
+      <c r="G97" s="17"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="14" t="s">
@@ -5310,34 +5313,34 @@
       <c r="D98" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" s="16" t="s">
         <v>288</v>
       </c>
       <c r="G98" s="14"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="17">
         <v>97.0</v>
       </c>
-      <c r="D99" s="16" t="s">
+      <c r="D99" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E99" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="F99" s="17" t="s">
+      <c r="F99" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="G99" s="16"/>
+      <c r="G99" s="17"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="14" t="s">
@@ -5352,55 +5355,55 @@
       <c r="D100" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E100" s="15" t="s">
+      <c r="E100" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="F100" s="15" t="s">
+      <c r="F100" s="16" t="s">
         <v>294</v>
       </c>
       <c r="G100" s="14"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="16" t="s">
+      <c r="A101" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="B101" s="16" t="s">
+      <c r="B101" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C101" s="16">
+      <c r="C101" s="17">
         <v>99.0</v>
       </c>
-      <c r="D101" s="16" t="s">
+      <c r="D101" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E101" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="G101" s="16"/>
+      <c r="G101" s="17"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="16" t="s">
+      <c r="A102" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B102" s="16" t="s">
+      <c r="B102" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="C102" s="16">
+      <c r="C102" s="17">
         <v>100.0</v>
       </c>
-      <c r="D102" s="16" t="s">
+      <c r="D102" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E102" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="F102" s="17" t="s">
+      <c r="F102" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="G102" s="16"/>
+      <c r="G102" s="17"/>
     </row>
     <row r="103" ht="15.75" customHeight="1"/>
     <row r="104" ht="15.75" customHeight="1"/>
@@ -6342,182 +6345,182 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22">
+      <c r="A2" s="15">
         <f t="shared" ref="A2:A11" si="1">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22">
+      <c r="A3" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>307</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22">
+      <c r="A4" s="15">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>310</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22">
+      <c r="A5" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="22">
+      <c r="A6" s="15">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>320</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="22">
+      <c r="A7" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="18" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22">
+      <c r="A8" s="15">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22">
+      <c r="A9" s="15">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="18" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22">
+      <c r="A10" s="15">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>333</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22">
+      <c r="A11" s="15">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="20" t="s">
         <v>340</v>
       </c>
     </row>
